--- a/quiz_questions.xlsx
+++ b/quiz_questions.xlsx
@@ -5,33 +5,22 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Toshi\ATP-app\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NB-AJLS\ATP-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47072E13-0F17-420C-B027-3B55A5AE62EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7A15EB9-51FA-4CCC-A4EA-891BB3F61F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5832" yWindow="708" windowWidth="16476" windowHeight="11532" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="337">
   <si>
     <t>カテゴリNo.</t>
   </si>
@@ -4344,17 +4333,35 @@
   </si>
   <si>
     <t>ざいりゅうカード</t>
+  </si>
+  <si>
+    <t>tes</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>drgs</t>
+  </si>
+  <si>
+    <t>sdfg</t>
+  </si>
+  <si>
+    <t>sdfgsd</t>
+  </si>
+  <si>
+    <t>sdfgsdfgs</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -4400,7 +4407,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="ＭＳ Ｐゴシック"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -4780,7 +4787,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -5022,9 +5029,12 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -5326,8 +5336,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V37"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="16.8" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:V38"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="3.88671875" style="1" customWidth="1"/>
     <col min="2" max="2" width="4.77734375" style="1" customWidth="1"/>
@@ -5341,7 +5351,7 @@
     <col min="21" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -5403,7 +5413,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:22" ht="70.05" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:22" ht="70.05" customHeight="1">
       <c r="A2" s="14">
         <v>1</v>
       </c>
@@ -5454,7 +5464,7 @@
       <c r="T2" s="72"/>
       <c r="V2"/>
     </row>
-    <row r="3" spans="1:22" ht="70.05" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:22" ht="70.05" customHeight="1">
       <c r="A3" s="21">
         <v>1</v>
       </c>
@@ -5501,7 +5511,7 @@
       <c r="T3" s="76"/>
       <c r="V3"/>
     </row>
-    <row r="4" spans="1:22" ht="70.05" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:22" ht="70.05" customHeight="1">
       <c r="A4" s="21">
         <v>1</v>
       </c>
@@ -5548,7 +5558,7 @@
       <c r="T4" s="76"/>
       <c r="V4"/>
     </row>
-    <row r="5" spans="1:22" ht="70.05" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" ht="70.05" customHeight="1">
       <c r="A5" s="21">
         <v>1</v>
       </c>
@@ -5599,7 +5609,7 @@
       <c r="T5" s="76"/>
       <c r="V5"/>
     </row>
-    <row r="6" spans="1:22" ht="70.05" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" ht="70.05" customHeight="1">
       <c r="A6" s="21">
         <v>1</v>
       </c>
@@ -5646,7 +5656,7 @@
       <c r="T6" s="76"/>
       <c r="V6"/>
     </row>
-    <row r="7" spans="1:22" ht="70.05" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" ht="70.05" customHeight="1">
       <c r="A7" s="21">
         <v>1</v>
       </c>
@@ -5693,7 +5703,7 @@
       <c r="T7" s="76"/>
       <c r="V7"/>
     </row>
-    <row r="8" spans="1:22" ht="70.05" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" ht="70.05" customHeight="1">
       <c r="A8" s="21">
         <v>1</v>
       </c>
@@ -5740,7 +5750,7 @@
       <c r="T8" s="76"/>
       <c r="V8"/>
     </row>
-    <row r="9" spans="1:22" ht="70.05" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" ht="70.05" customHeight="1">
       <c r="A9" s="21">
         <v>1</v>
       </c>
@@ -5795,7 +5805,7 @@
       <c r="T9" s="76"/>
       <c r="V9"/>
     </row>
-    <row r="10" spans="1:22" ht="70.05" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" ht="70.05" customHeight="1">
       <c r="A10" s="21">
         <v>1</v>
       </c>
@@ -5850,7 +5860,7 @@
       </c>
       <c r="V10"/>
     </row>
-    <row r="11" spans="1:22" ht="70.05" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" ht="70.05" customHeight="1">
       <c r="A11" s="21">
         <v>1</v>
       </c>
@@ -5901,7 +5911,7 @@
       <c r="T11" s="76"/>
       <c r="V11"/>
     </row>
-    <row r="12" spans="1:22" ht="70.05" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:22" ht="70.05" customHeight="1">
       <c r="A12" s="21">
         <v>1</v>
       </c>
@@ -5956,7 +5966,7 @@
       </c>
       <c r="V12"/>
     </row>
-    <row r="13" spans="1:22" ht="70.05" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:22" ht="70.05" customHeight="1">
       <c r="A13" s="21">
         <v>1</v>
       </c>
@@ -6007,7 +6017,7 @@
       <c r="T13" s="76"/>
       <c r="V13"/>
     </row>
-    <row r="14" spans="1:22" ht="70.05" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:22" ht="70.05" customHeight="1">
       <c r="A14" s="21">
         <v>1</v>
       </c>
@@ -6066,7 +6076,7 @@
       </c>
       <c r="V14"/>
     </row>
-    <row r="15" spans="1:22" ht="70.05" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:22" ht="70.05" customHeight="1">
       <c r="A15" s="21">
         <v>1</v>
       </c>
@@ -6121,7 +6131,7 @@
       </c>
       <c r="V15"/>
     </row>
-    <row r="16" spans="1:22" ht="70.05" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:22" ht="70.05" customHeight="1">
       <c r="A16" s="21">
         <v>1</v>
       </c>
@@ -6176,7 +6186,7 @@
       </c>
       <c r="V16"/>
     </row>
-    <row r="17" spans="1:22" ht="70.05" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:22" ht="70.05" customHeight="1">
       <c r="A17" s="21">
         <v>1</v>
       </c>
@@ -6221,7 +6231,7 @@
       <c r="T17" s="76"/>
       <c r="V17"/>
     </row>
-    <row r="18" spans="1:22" ht="70.05" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:22" ht="70.05" customHeight="1">
       <c r="A18" s="21">
         <v>1</v>
       </c>
@@ -6266,7 +6276,7 @@
       <c r="T18" s="76"/>
       <c r="V18"/>
     </row>
-    <row r="19" spans="1:22" ht="70.05" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:22" ht="70.05" customHeight="1">
       <c r="A19" s="21">
         <v>1</v>
       </c>
@@ -6317,7 +6327,7 @@
       <c r="T19" s="76"/>
       <c r="V19"/>
     </row>
-    <row r="20" spans="1:22" ht="70.05" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:22" ht="70.05" customHeight="1">
       <c r="A20" s="21">
         <v>1</v>
       </c>
@@ -6368,7 +6378,7 @@
       <c r="T20" s="76"/>
       <c r="V20"/>
     </row>
-    <row r="21" spans="1:22" ht="70.05" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:22" ht="70.05" customHeight="1">
       <c r="A21" s="21">
         <v>1</v>
       </c>
@@ -6415,7 +6425,7 @@
       <c r="T21" s="76"/>
       <c r="V21"/>
     </row>
-    <row r="22" spans="1:22" ht="70.05" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:22" ht="70.05" customHeight="1">
       <c r="A22" s="21">
         <v>1</v>
       </c>
@@ -6462,7 +6472,7 @@
       <c r="T22" s="76"/>
       <c r="V22"/>
     </row>
-    <row r="23" spans="1:22" ht="70.05" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:22" ht="70.05" customHeight="1">
       <c r="A23" s="21">
         <v>1</v>
       </c>
@@ -6509,7 +6519,7 @@
       <c r="T23" s="76"/>
       <c r="V23"/>
     </row>
-    <row r="24" spans="1:22" ht="70.05" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:22" ht="70.05" customHeight="1">
       <c r="A24" s="21">
         <v>1</v>
       </c>
@@ -6556,7 +6566,7 @@
       <c r="T24" s="76"/>
       <c r="V24"/>
     </row>
-    <row r="25" spans="1:22" ht="70.05" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:22" ht="70.05" customHeight="1">
       <c r="A25" s="21">
         <v>2</v>
       </c>
@@ -6611,7 +6621,7 @@
       </c>
       <c r="V25"/>
     </row>
-    <row r="26" spans="1:22" ht="70.05" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:22" ht="70.05" customHeight="1">
       <c r="A26" s="21">
         <v>2</v>
       </c>
@@ -6666,7 +6676,7 @@
       </c>
       <c r="V26"/>
     </row>
-    <row r="27" spans="1:22" ht="70.05" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:22" ht="70.05" customHeight="1">
       <c r="A27" s="21">
         <v>2</v>
       </c>
@@ -6717,7 +6727,7 @@
       <c r="T27" s="76"/>
       <c r="V27"/>
     </row>
-    <row r="28" spans="1:22" ht="70.05" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:22" ht="70.05" customHeight="1">
       <c r="A28" s="21">
         <v>2</v>
       </c>
@@ -6768,7 +6778,7 @@
       <c r="T28" s="76"/>
       <c r="V28"/>
     </row>
-    <row r="29" spans="1:22" ht="70.05" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:22" ht="70.05" customHeight="1">
       <c r="A29" s="21">
         <v>2</v>
       </c>
@@ -6819,7 +6829,7 @@
       <c r="T29" s="76"/>
       <c r="V29"/>
     </row>
-    <row r="30" spans="1:22" ht="70.05" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:22" ht="70.05" customHeight="1">
       <c r="A30" s="21">
         <v>2</v>
       </c>
@@ -6870,7 +6880,7 @@
       <c r="T30" s="76"/>
       <c r="V30"/>
     </row>
-    <row r="31" spans="1:22" ht="70.05" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:22" ht="70.05" customHeight="1">
       <c r="A31" s="21">
         <v>2</v>
       </c>
@@ -6921,7 +6931,7 @@
       <c r="T31" s="76"/>
       <c r="V31"/>
     </row>
-    <row r="32" spans="1:22" ht="70.05" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:22" ht="70.05" customHeight="1">
       <c r="A32" s="21">
         <v>2</v>
       </c>
@@ -6968,7 +6978,7 @@
       <c r="T32" s="76"/>
       <c r="V32"/>
     </row>
-    <row r="33" spans="1:22" ht="70.05" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:22" ht="70.05" customHeight="1">
       <c r="A33" s="21">
         <v>2</v>
       </c>
@@ -7015,7 +7025,7 @@
       <c r="T33" s="76"/>
       <c r="V33"/>
     </row>
-    <row r="34" spans="1:22" ht="70.05" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:22" ht="70.05" customHeight="1">
       <c r="A34" s="21">
         <v>2</v>
       </c>
@@ -7066,7 +7076,7 @@
       <c r="T34" s="76"/>
       <c r="V34"/>
     </row>
-    <row r="35" spans="1:22" ht="70.05" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:22" ht="70.05" customHeight="1">
       <c r="A35" s="21">
         <v>2</v>
       </c>
@@ -7113,7 +7123,7 @@
       <c r="T35" s="76"/>
       <c r="V35"/>
     </row>
-    <row r="36" spans="1:22" ht="70.05" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:22" ht="70.05" customHeight="1">
       <c r="A36" s="21">
         <v>2</v>
       </c>
@@ -7164,7 +7174,7 @@
       <c r="T36" s="76"/>
       <c r="V36"/>
     </row>
-    <row r="37" spans="1:22" ht="70.05" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:22" ht="70.05" customHeight="1">
       <c r="A37" s="29">
         <v>2</v>
       </c>
@@ -7209,6 +7219,51 @@
       <c r="T37" s="80"/>
       <c r="V37"/>
     </row>
+    <row r="38" spans="1:22" ht="70.05" customHeight="1">
+      <c r="A38" s="29">
+        <v>2</v>
+      </c>
+      <c r="B38" s="30">
+        <v>14</v>
+      </c>
+      <c r="C38" s="31" t="s">
+        <v>219</v>
+      </c>
+      <c r="D38" s="32" t="s">
+        <v>220</v>
+      </c>
+      <c r="E38" s="33" t="s">
+        <v>331</v>
+      </c>
+      <c r="F38" s="81" t="s">
+        <v>332</v>
+      </c>
+      <c r="G38" s="35" t="s">
+        <v>333</v>
+      </c>
+      <c r="H38" s="36"/>
+      <c r="I38" s="57"/>
+      <c r="J38" s="58"/>
+      <c r="K38" s="59"/>
+      <c r="L38" s="60"/>
+      <c r="M38" s="61" t="s">
+        <v>334</v>
+      </c>
+      <c r="N38" s="62" t="s">
+        <v>335</v>
+      </c>
+      <c r="O38" s="63" t="s">
+        <v>336</v>
+      </c>
+      <c r="P38" s="64"/>
+      <c r="Q38" s="77"/>
+      <c r="R38" s="78" t="s">
+        <v>330</v>
+      </c>
+      <c r="S38" s="79"/>
+      <c r="T38" s="80"/>
+      <c r="V38"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/quiz_questions.xlsx
+++ b/quiz_questions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NB-AJLS\ATP-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7A15EB9-51FA-4CCC-A4EA-891BB3F61F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E516E1B-25C9-48C4-86E8-6CD02565C919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10500" yWindow="972" windowWidth="12372" windowHeight="10812" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="339">
   <si>
     <t>カテゴリNo.</t>
   </si>
@@ -4351,6 +4351,12 @@
   </si>
   <si>
     <t>sdfgsdfgs</t>
+  </si>
+  <si>
+    <t>add</t>
+  </si>
+  <si>
+    <t>ADD</t>
   </si>
 </sst>
 </file>
@@ -7221,16 +7227,16 @@
     </row>
     <row r="38" spans="1:22" ht="70.05" customHeight="1">
       <c r="A38" s="29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B38" s="30">
         <v>14</v>
       </c>
       <c r="C38" s="31" t="s">
-        <v>219</v>
+        <v>337</v>
       </c>
       <c r="D38" s="32" t="s">
-        <v>220</v>
+        <v>338</v>
       </c>
       <c r="E38" s="33" t="s">
         <v>331</v>

--- a/quiz_questions.xlsx
+++ b/quiz_questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NB-AJLS\ATP-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E516E1B-25C9-48C4-86E8-6CD02565C919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7943CF2B-FFD2-4A02-BFD4-0CAE17CC1573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10500" yWindow="972" windowWidth="12372" windowHeight="10812" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="331">
   <si>
     <t>カテゴリNo.</t>
   </si>
@@ -4333,30 +4333,6 @@
   </si>
   <si>
     <t>ざいりゅうカード</t>
-  </si>
-  <si>
-    <t>tes</t>
-  </si>
-  <si>
-    <t>test</t>
-  </si>
-  <si>
-    <t>drgs</t>
-  </si>
-  <si>
-    <t>sdfg</t>
-  </si>
-  <si>
-    <t>sdfgsd</t>
-  </si>
-  <si>
-    <t>sdfgsdfgs</t>
-  </si>
-  <si>
-    <t>add</t>
-  </si>
-  <si>
-    <t>ADD</t>
   </si>
 </sst>
 </file>
@@ -4793,7 +4769,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -5033,9 +5009,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5342,7 +5315,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V38"/>
+  <dimension ref="A1:V37"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="3.88671875" style="1" customWidth="1"/>
@@ -7225,51 +7198,6 @@
       <c r="T37" s="80"/>
       <c r="V37"/>
     </row>
-    <row r="38" spans="1:22" ht="70.05" customHeight="1">
-      <c r="A38" s="29">
-        <v>3</v>
-      </c>
-      <c r="B38" s="30">
-        <v>14</v>
-      </c>
-      <c r="C38" s="31" t="s">
-        <v>337</v>
-      </c>
-      <c r="D38" s="32" t="s">
-        <v>338</v>
-      </c>
-      <c r="E38" s="33" t="s">
-        <v>331</v>
-      </c>
-      <c r="F38" s="81" t="s">
-        <v>332</v>
-      </c>
-      <c r="G38" s="35" t="s">
-        <v>333</v>
-      </c>
-      <c r="H38" s="36"/>
-      <c r="I38" s="57"/>
-      <c r="J38" s="58"/>
-      <c r="K38" s="59"/>
-      <c r="L38" s="60"/>
-      <c r="M38" s="61" t="s">
-        <v>334</v>
-      </c>
-      <c r="N38" s="62" t="s">
-        <v>335</v>
-      </c>
-      <c r="O38" s="63" t="s">
-        <v>336</v>
-      </c>
-      <c r="P38" s="64"/>
-      <c r="Q38" s="77"/>
-      <c r="R38" s="78" t="s">
-        <v>330</v>
-      </c>
-      <c r="S38" s="79"/>
-      <c r="T38" s="80"/>
-      <c r="V38"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/quiz_questions.xlsx
+++ b/quiz_questions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NB-AJLS\ATP-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7943CF2B-FFD2-4A02-BFD4-0CAE17CC1573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC0B3785-BB8C-4E12-AE6E-C186C0AE96AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10500" yWindow="972" windowWidth="12372" windowHeight="10812" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4068" yWindow="1092" windowWidth="12372" windowHeight="10812" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="335">
   <si>
     <t>カテゴリNo.</t>
   </si>
@@ -4333,6 +4333,18 @@
   </si>
   <si>
     <t>ざいりゅうカード</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>eterg</t>
+  </si>
+  <si>
+    <t>ttest</t>
+  </si>
+  <si>
+    <t>tesr</t>
   </si>
 </sst>
 </file>
@@ -4769,7 +4781,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -5009,6 +5021,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5315,7 +5333,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V37"/>
+  <dimension ref="A1:V39"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="3.88671875" style="1" customWidth="1"/>
@@ -6547,57 +6565,49 @@
     </row>
     <row r="25" spans="1:22" ht="70.05" customHeight="1">
       <c r="A25" s="21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B25" s="21">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C25" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D25" s="28" t="s">
-        <v>220</v>
+        <v>20</v>
+      </c>
+      <c r="D25" s="23" t="s">
+        <v>21</v>
       </c>
       <c r="E25" s="24" t="s">
-        <v>221</v>
-      </c>
-      <c r="F25" s="25" t="s">
-        <v>222</v>
+        <v>333</v>
+      </c>
+      <c r="F25" s="82" t="s">
+        <v>334</v>
       </c>
       <c r="G25" s="26" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>224</v>
-      </c>
-      <c r="I25" s="51" t="s">
-        <v>225</v>
-      </c>
-      <c r="J25" s="20" t="s">
-        <v>226</v>
-      </c>
-      <c r="K25" s="52" t="s">
-        <v>227</v>
-      </c>
-      <c r="L25" s="46" t="s">
-        <v>228</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="I25" s="51"/>
+      <c r="J25" s="20"/>
+      <c r="K25" s="52"/>
+      <c r="L25" s="46"/>
       <c r="M25" s="53" t="s">
-        <v>229</v>
-      </c>
-      <c r="N25" s="54"/>
-      <c r="O25" s="55"/>
+        <v>216</v>
+      </c>
+      <c r="N25" s="54" t="s">
+        <v>217</v>
+      </c>
+      <c r="O25" s="55" t="s">
+        <v>218</v>
+      </c>
       <c r="P25" s="56"/>
       <c r="Q25" s="73"/>
       <c r="R25" s="74" t="s">
-        <v>223</v>
-      </c>
-      <c r="S25" s="75" t="s">
-        <v>225</v>
-      </c>
-      <c r="T25" s="76" t="s">
-        <v>227</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="S25" s="75"/>
+      <c r="T25" s="76"/>
       <c r="V25"/>
     </row>
     <row r="26" spans="1:22" ht="70.05" customHeight="1">
@@ -6605,7 +6615,7 @@
         <v>2</v>
       </c>
       <c r="B26" s="21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26" s="22" t="s">
         <v>219</v>
@@ -6614,44 +6624,44 @@
         <v>220</v>
       </c>
       <c r="E26" s="24" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="F26" s="25" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="G26" s="26" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="I26" s="51" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="J26" s="20" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="K26" s="52" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="L26" s="46" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="M26" s="53" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="N26" s="54"/>
       <c r="O26" s="55"/>
       <c r="P26" s="56"/>
       <c r="Q26" s="73"/>
       <c r="R26" s="74" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="S26" s="75" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="T26" s="76" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="V26"/>
     </row>
@@ -6660,7 +6670,7 @@
         <v>2</v>
       </c>
       <c r="B27" s="21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C27" s="22" t="s">
         <v>219</v>
@@ -6669,41 +6679,45 @@
         <v>220</v>
       </c>
       <c r="E27" s="24" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="F27" s="25" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="G27" s="26" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="I27" s="51" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="J27" s="20" t="s">
-        <v>246</v>
-      </c>
-      <c r="K27" s="52"/>
-      <c r="L27" s="46"/>
+        <v>235</v>
+      </c>
+      <c r="K27" s="52" t="s">
+        <v>236</v>
+      </c>
+      <c r="L27" s="46" t="s">
+        <v>237</v>
+      </c>
       <c r="M27" s="53" t="s">
-        <v>247</v>
-      </c>
-      <c r="N27" s="54" t="s">
-        <v>248</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="N27" s="54"/>
       <c r="O27" s="55"/>
       <c r="P27" s="56"/>
       <c r="Q27" s="73"/>
       <c r="R27" s="74" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="S27" s="75" t="s">
-        <v>245</v>
-      </c>
-      <c r="T27" s="76"/>
+        <v>234</v>
+      </c>
+      <c r="T27" s="76" t="s">
+        <v>240</v>
+      </c>
       <c r="V27"/>
     </row>
     <row r="28" spans="1:22" ht="70.05" customHeight="1">
@@ -6711,7 +6725,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C28" s="22" t="s">
         <v>219</v>
@@ -6720,39 +6734,39 @@
         <v>220</v>
       </c>
       <c r="E28" s="24" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="F28" s="25" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="G28" s="26" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="H28" s="20" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="I28" s="51" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="J28" s="20" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="K28" s="52"/>
       <c r="L28" s="46"/>
       <c r="M28" s="53" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="N28" s="54" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="O28" s="55"/>
       <c r="P28" s="56"/>
       <c r="Q28" s="73"/>
       <c r="R28" s="74" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="S28" s="75" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="T28" s="76"/>
       <c r="V28"/>
@@ -6762,7 +6776,7 @@
         <v>2</v>
       </c>
       <c r="B29" s="21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C29" s="22" t="s">
         <v>219</v>
@@ -6771,39 +6785,39 @@
         <v>220</v>
       </c>
       <c r="E29" s="24" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="F29" s="25" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="G29" s="26" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="I29" s="51" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="J29" s="20" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="K29" s="52"/>
       <c r="L29" s="46"/>
       <c r="M29" s="53" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="N29" s="54" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="O29" s="55"/>
       <c r="P29" s="56"/>
       <c r="Q29" s="73"/>
       <c r="R29" s="74" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="S29" s="75" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="T29" s="76"/>
       <c r="V29"/>
@@ -6813,7 +6827,7 @@
         <v>2</v>
       </c>
       <c r="B30" s="21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C30" s="22" t="s">
         <v>219</v>
@@ -6822,39 +6836,39 @@
         <v>220</v>
       </c>
       <c r="E30" s="24" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="F30" s="25" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="G30" s="26" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="H30" s="20" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="I30" s="51" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="J30" s="20" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="K30" s="52"/>
       <c r="L30" s="46"/>
       <c r="M30" s="53" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="N30" s="54" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="O30" s="55"/>
       <c r="P30" s="56"/>
       <c r="Q30" s="73"/>
       <c r="R30" s="74" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="S30" s="75" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="T30" s="76"/>
       <c r="V30"/>
@@ -6864,7 +6878,7 @@
         <v>2</v>
       </c>
       <c r="B31" s="21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C31" s="22" t="s">
         <v>219</v>
@@ -6873,39 +6887,39 @@
         <v>220</v>
       </c>
       <c r="E31" s="24" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="F31" s="25" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="G31" s="26" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="H31" s="20" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="I31" s="51" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="J31" s="20" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="K31" s="52"/>
       <c r="L31" s="46"/>
       <c r="M31" s="53" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="N31" s="54" t="s">
-        <v>256</v>
+        <v>275</v>
       </c>
       <c r="O31" s="55"/>
       <c r="P31" s="56"/>
       <c r="Q31" s="73"/>
       <c r="R31" s="74" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="S31" s="75" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="T31" s="76"/>
       <c r="V31"/>
@@ -6915,7 +6929,7 @@
         <v>2</v>
       </c>
       <c r="B32" s="21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C32" s="22" t="s">
         <v>219</v>
@@ -6924,36 +6938,40 @@
         <v>220</v>
       </c>
       <c r="E32" s="24" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="F32" s="25" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="G32" s="26" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="H32" s="20" t="s">
-        <v>287</v>
-      </c>
-      <c r="I32" s="51"/>
-      <c r="J32" s="20"/>
+        <v>279</v>
+      </c>
+      <c r="I32" s="51" t="s">
+        <v>280</v>
+      </c>
+      <c r="J32" s="20" t="s">
+        <v>281</v>
+      </c>
       <c r="K32" s="52"/>
       <c r="L32" s="46"/>
       <c r="M32" s="53" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="N32" s="54" t="s">
-        <v>289</v>
-      </c>
-      <c r="O32" s="55" t="s">
-        <v>290</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="O32" s="55"/>
       <c r="P32" s="56"/>
       <c r="Q32" s="73"/>
       <c r="R32" s="74" t="s">
-        <v>286</v>
-      </c>
-      <c r="S32" s="75"/>
+        <v>278</v>
+      </c>
+      <c r="S32" s="75" t="s">
+        <v>283</v>
+      </c>
       <c r="T32" s="76"/>
       <c r="V32"/>
     </row>
@@ -6962,7 +6980,7 @@
         <v>2</v>
       </c>
       <c r="B33" s="21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C33" s="22" t="s">
         <v>219</v>
@@ -6971,34 +6989,34 @@
         <v>220</v>
       </c>
       <c r="E33" s="24" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="F33" s="25" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="G33" s="26" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="H33" s="20" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="I33" s="51"/>
       <c r="J33" s="20"/>
       <c r="K33" s="52"/>
       <c r="L33" s="46"/>
       <c r="M33" s="53" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="N33" s="54" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="O33" s="55" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="P33" s="56"/>
       <c r="Q33" s="73"/>
       <c r="R33" s="74" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="S33" s="75"/>
       <c r="T33" s="76"/>
@@ -7009,7 +7027,7 @@
         <v>2</v>
       </c>
       <c r="B34" s="21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C34" s="22" t="s">
         <v>219</v>
@@ -7018,40 +7036,36 @@
         <v>220</v>
       </c>
       <c r="E34" s="24" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="F34" s="25" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="G34" s="26" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="H34" s="20" t="s">
-        <v>302</v>
-      </c>
-      <c r="I34" s="51" t="s">
-        <v>303</v>
-      </c>
-      <c r="J34" s="20" t="s">
-        <v>304</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="I34" s="51"/>
+      <c r="J34" s="20"/>
       <c r="K34" s="52"/>
       <c r="L34" s="46"/>
       <c r="M34" s="53" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="N34" s="54" t="s">
-        <v>306</v>
-      </c>
-      <c r="O34" s="55"/>
+        <v>296</v>
+      </c>
+      <c r="O34" s="55" t="s">
+        <v>297</v>
+      </c>
       <c r="P34" s="56"/>
       <c r="Q34" s="73"/>
       <c r="R34" s="74" t="s">
-        <v>301</v>
-      </c>
-      <c r="S34" s="75" t="s">
-        <v>307</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="S34" s="75"/>
       <c r="T34" s="76"/>
       <c r="V34"/>
     </row>
@@ -7060,7 +7074,7 @@
         <v>2</v>
       </c>
       <c r="B35" s="21">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C35" s="22" t="s">
         <v>219</v>
@@ -7069,36 +7083,40 @@
         <v>220</v>
       </c>
       <c r="E35" s="24" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="F35" s="25" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="G35" s="26" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="H35" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="I35" s="51"/>
-      <c r="J35" s="20"/>
+        <v>302</v>
+      </c>
+      <c r="I35" s="51" t="s">
+        <v>303</v>
+      </c>
+      <c r="J35" s="20" t="s">
+        <v>304</v>
+      </c>
       <c r="K35" s="52"/>
       <c r="L35" s="46"/>
       <c r="M35" s="53" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="N35" s="54" t="s">
-        <v>313</v>
-      </c>
-      <c r="O35" s="55" t="s">
-        <v>314</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="O35" s="55"/>
       <c r="P35" s="56"/>
       <c r="Q35" s="73"/>
       <c r="R35" s="74" t="s">
-        <v>310</v>
-      </c>
-      <c r="S35" s="75"/>
+        <v>301</v>
+      </c>
+      <c r="S35" s="75" t="s">
+        <v>307</v>
+      </c>
       <c r="T35" s="76"/>
       <c r="V35"/>
     </row>
@@ -7107,7 +7125,7 @@
         <v>2</v>
       </c>
       <c r="B36" s="21">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C36" s="22" t="s">
         <v>219</v>
@@ -7116,87 +7134,179 @@
         <v>220</v>
       </c>
       <c r="E36" s="24" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="F36" s="25" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="G36" s="26" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="H36" s="20" t="s">
-        <v>318</v>
-      </c>
-      <c r="I36" s="51" t="s">
-        <v>319</v>
-      </c>
-      <c r="J36" s="20" t="s">
-        <v>320</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="I36" s="51"/>
+      <c r="J36" s="20"/>
       <c r="K36" s="52"/>
       <c r="L36" s="46"/>
       <c r="M36" s="53" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="N36" s="54" t="s">
-        <v>322</v>
-      </c>
-      <c r="O36" s="55"/>
+        <v>313</v>
+      </c>
+      <c r="O36" s="55" t="s">
+        <v>314</v>
+      </c>
       <c r="P36" s="56"/>
       <c r="Q36" s="73"/>
       <c r="R36" s="74" t="s">
-        <v>317</v>
-      </c>
-      <c r="S36" s="75" t="s">
-        <v>323</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="S36" s="75"/>
       <c r="T36" s="76"/>
       <c r="V36"/>
     </row>
     <row r="37" spans="1:22" ht="70.05" customHeight="1">
-      <c r="A37" s="29">
+      <c r="A37" s="21">
         <v>2</v>
       </c>
-      <c r="B37" s="30">
+      <c r="B37" s="21">
+        <v>12</v>
+      </c>
+      <c r="C37" s="22" t="s">
+        <v>219</v>
+      </c>
+      <c r="D37" s="28" t="s">
+        <v>220</v>
+      </c>
+      <c r="E37" s="24" t="s">
+        <v>315</v>
+      </c>
+      <c r="F37" s="25" t="s">
+        <v>316</v>
+      </c>
+      <c r="G37" s="26" t="s">
+        <v>317</v>
+      </c>
+      <c r="H37" s="20" t="s">
+        <v>318</v>
+      </c>
+      <c r="I37" s="51" t="s">
+        <v>319</v>
+      </c>
+      <c r="J37" s="20" t="s">
+        <v>320</v>
+      </c>
+      <c r="K37" s="52"/>
+      <c r="L37" s="46"/>
+      <c r="M37" s="53" t="s">
+        <v>321</v>
+      </c>
+      <c r="N37" s="54" t="s">
+        <v>322</v>
+      </c>
+      <c r="O37" s="55"/>
+      <c r="P37" s="56"/>
+      <c r="Q37" s="73"/>
+      <c r="R37" s="74" t="s">
+        <v>317</v>
+      </c>
+      <c r="S37" s="75" t="s">
+        <v>323</v>
+      </c>
+      <c r="T37" s="76"/>
+      <c r="V37"/>
+    </row>
+    <row r="38" spans="1:22" ht="70.05" customHeight="1">
+      <c r="A38" s="29">
+        <v>2</v>
+      </c>
+      <c r="B38" s="30">
         <v>13</v>
       </c>
-      <c r="C37" s="31" t="s">
+      <c r="C38" s="31" t="s">
         <v>219</v>
       </c>
-      <c r="D37" s="32" t="s">
+      <c r="D38" s="32" t="s">
         <v>220</v>
       </c>
-      <c r="E37" s="33" t="s">
+      <c r="E38" s="33" t="s">
         <v>324</v>
       </c>
-      <c r="F37" s="34" t="s">
+      <c r="F38" s="34" t="s">
         <v>325</v>
       </c>
-      <c r="G37" s="35" t="s">
+      <c r="G38" s="35" t="s">
         <v>326</v>
       </c>
-      <c r="H37" s="36"/>
-      <c r="I37" s="57"/>
-      <c r="J37" s="58"/>
-      <c r="K37" s="59"/>
-      <c r="L37" s="60"/>
-      <c r="M37" s="61" t="s">
+      <c r="H38" s="36"/>
+      <c r="I38" s="57"/>
+      <c r="J38" s="58"/>
+      <c r="K38" s="59"/>
+      <c r="L38" s="60"/>
+      <c r="M38" s="61" t="s">
         <v>327</v>
       </c>
-      <c r="N37" s="62" t="s">
+      <c r="N38" s="62" t="s">
         <v>328</v>
       </c>
-      <c r="O37" s="63" t="s">
+      <c r="O38" s="63" t="s">
         <v>329</v>
       </c>
-      <c r="P37" s="64"/>
-      <c r="Q37" s="77"/>
-      <c r="R37" s="78" t="s">
+      <c r="P38" s="64"/>
+      <c r="Q38" s="77"/>
+      <c r="R38" s="78" t="s">
         <v>330</v>
       </c>
-      <c r="S37" s="79"/>
-      <c r="T37" s="80"/>
-      <c r="V37"/>
+      <c r="S38" s="79"/>
+      <c r="T38" s="80"/>
+      <c r="V38"/>
+    </row>
+    <row r="39" spans="1:22" ht="70.05" customHeight="1">
+      <c r="A39" s="29">
+        <v>2</v>
+      </c>
+      <c r="B39" s="30">
+        <v>14</v>
+      </c>
+      <c r="C39" s="31" t="s">
+        <v>219</v>
+      </c>
+      <c r="D39" s="32" t="s">
+        <v>220</v>
+      </c>
+      <c r="E39" s="33" t="s">
+        <v>331</v>
+      </c>
+      <c r="F39" s="81" t="s">
+        <v>332</v>
+      </c>
+      <c r="G39" s="35" t="s">
+        <v>326</v>
+      </c>
+      <c r="H39" s="36"/>
+      <c r="I39" s="57"/>
+      <c r="J39" s="58"/>
+      <c r="K39" s="59"/>
+      <c r="L39" s="60"/>
+      <c r="M39" s="61" t="s">
+        <v>327</v>
+      </c>
+      <c r="N39" s="62" t="s">
+        <v>328</v>
+      </c>
+      <c r="O39" s="63" t="s">
+        <v>329</v>
+      </c>
+      <c r="P39" s="64"/>
+      <c r="Q39" s="77"/>
+      <c r="R39" s="78" t="s">
+        <v>330</v>
+      </c>
+      <c r="S39" s="79"/>
+      <c r="T39" s="80"/>
+      <c r="V39"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7"/>

--- a/quiz_questions.xlsx
+++ b/quiz_questions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NB-AJLS\ATP-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC0B3785-BB8C-4E12-AE6E-C186C0AE96AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97E4C518-2FFC-405E-B5ED-B177118EBE7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4068" yWindow="1092" windowWidth="12372" windowHeight="10812" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1116" yWindow="1116" windowWidth="12372" windowHeight="10812" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="331">
   <si>
     <t>カテゴリNo.</t>
   </si>
@@ -4333,18 +4333,6 @@
   </si>
   <si>
     <t>ざいりゅうカード</t>
-  </si>
-  <si>
-    <t>test</t>
-  </si>
-  <si>
-    <t>eterg</t>
-  </si>
-  <si>
-    <t>ttest</t>
-  </si>
-  <si>
-    <t>tesr</t>
   </si>
 </sst>
 </file>
@@ -4781,7 +4769,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -5021,12 +5009,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5333,7 +5315,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V39"/>
+  <dimension ref="A1:V37"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="3.88671875" style="1" customWidth="1"/>
@@ -6565,49 +6547,57 @@
     </row>
     <row r="25" spans="1:22" ht="70.05" customHeight="1">
       <c r="A25" s="21">
+        <v>2</v>
+      </c>
+      <c r="B25" s="21">
         <v>1</v>
       </c>
-      <c r="B25" s="21">
-        <v>24</v>
-      </c>
       <c r="C25" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="D25" s="23" t="s">
-        <v>21</v>
+        <v>219</v>
+      </c>
+      <c r="D25" s="28" t="s">
+        <v>220</v>
       </c>
       <c r="E25" s="24" t="s">
-        <v>333</v>
-      </c>
-      <c r="F25" s="82" t="s">
-        <v>334</v>
+        <v>221</v>
+      </c>
+      <c r="F25" s="25" t="s">
+        <v>222</v>
       </c>
       <c r="G25" s="26" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>215</v>
-      </c>
-      <c r="I25" s="51"/>
-      <c r="J25" s="20"/>
-      <c r="K25" s="52"/>
-      <c r="L25" s="46"/>
+        <v>224</v>
+      </c>
+      <c r="I25" s="51" t="s">
+        <v>225</v>
+      </c>
+      <c r="J25" s="20" t="s">
+        <v>226</v>
+      </c>
+      <c r="K25" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="L25" s="46" t="s">
+        <v>228</v>
+      </c>
       <c r="M25" s="53" t="s">
-        <v>216</v>
-      </c>
-      <c r="N25" s="54" t="s">
-        <v>217</v>
-      </c>
-      <c r="O25" s="55" t="s">
-        <v>218</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="N25" s="54"/>
+      <c r="O25" s="55"/>
       <c r="P25" s="56"/>
       <c r="Q25" s="73"/>
       <c r="R25" s="74" t="s">
-        <v>214</v>
-      </c>
-      <c r="S25" s="75"/>
-      <c r="T25" s="76"/>
+        <v>223</v>
+      </c>
+      <c r="S25" s="75" t="s">
+        <v>225</v>
+      </c>
+      <c r="T25" s="76" t="s">
+        <v>227</v>
+      </c>
       <c r="V25"/>
     </row>
     <row r="26" spans="1:22" ht="70.05" customHeight="1">
@@ -6615,7 +6605,7 @@
         <v>2</v>
       </c>
       <c r="B26" s="21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C26" s="22" t="s">
         <v>219</v>
@@ -6624,44 +6614,44 @@
         <v>220</v>
       </c>
       <c r="E26" s="24" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="F26" s="25" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="G26" s="26" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="I26" s="51" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="J26" s="20" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="K26" s="52" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="L26" s="46" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="M26" s="53" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="N26" s="54"/>
       <c r="O26" s="55"/>
       <c r="P26" s="56"/>
       <c r="Q26" s="73"/>
       <c r="R26" s="74" t="s">
-        <v>223</v>
+        <v>239</v>
       </c>
       <c r="S26" s="75" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="T26" s="76" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="V26"/>
     </row>
@@ -6670,7 +6660,7 @@
         <v>2</v>
       </c>
       <c r="B27" s="21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C27" s="22" t="s">
         <v>219</v>
@@ -6679,45 +6669,41 @@
         <v>220</v>
       </c>
       <c r="E27" s="24" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="F27" s="25" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="G27" s="26" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="I27" s="51" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="J27" s="20" t="s">
-        <v>235</v>
-      </c>
-      <c r="K27" s="52" t="s">
-        <v>236</v>
-      </c>
-      <c r="L27" s="46" t="s">
-        <v>237</v>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="K27" s="52"/>
+      <c r="L27" s="46"/>
       <c r="M27" s="53" t="s">
-        <v>238</v>
-      </c>
-      <c r="N27" s="54"/>
+        <v>247</v>
+      </c>
+      <c r="N27" s="54" t="s">
+        <v>248</v>
+      </c>
       <c r="O27" s="55"/>
       <c r="P27" s="56"/>
       <c r="Q27" s="73"/>
       <c r="R27" s="74" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="S27" s="75" t="s">
-        <v>234</v>
-      </c>
-      <c r="T27" s="76" t="s">
-        <v>240</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="T27" s="76"/>
       <c r="V27"/>
     </row>
     <row r="28" spans="1:22" ht="70.05" customHeight="1">
@@ -6725,7 +6711,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C28" s="22" t="s">
         <v>219</v>
@@ -6734,39 +6720,39 @@
         <v>220</v>
       </c>
       <c r="E28" s="24" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="F28" s="25" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="G28" s="26" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="H28" s="20" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="I28" s="51" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="J28" s="20" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="K28" s="52"/>
       <c r="L28" s="46"/>
       <c r="M28" s="53" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="N28" s="54" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="O28" s="55"/>
       <c r="P28" s="56"/>
       <c r="Q28" s="73"/>
       <c r="R28" s="74" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="S28" s="75" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="T28" s="76"/>
       <c r="V28"/>
@@ -6776,7 +6762,7 @@
         <v>2</v>
       </c>
       <c r="B29" s="21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C29" s="22" t="s">
         <v>219</v>
@@ -6785,39 +6771,39 @@
         <v>220</v>
       </c>
       <c r="E29" s="24" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="F29" s="25" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="G29" s="26" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="I29" s="51" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="J29" s="20" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="K29" s="52"/>
       <c r="L29" s="46"/>
       <c r="M29" s="53" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="N29" s="54" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="O29" s="55"/>
       <c r="P29" s="56"/>
       <c r="Q29" s="73"/>
       <c r="R29" s="74" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="S29" s="75" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="T29" s="76"/>
       <c r="V29"/>
@@ -6827,7 +6813,7 @@
         <v>2</v>
       </c>
       <c r="B30" s="21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C30" s="22" t="s">
         <v>219</v>
@@ -6836,39 +6822,39 @@
         <v>220</v>
       </c>
       <c r="E30" s="24" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="F30" s="25" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="G30" s="26" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="H30" s="20" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="I30" s="51" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="J30" s="20" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="K30" s="52"/>
       <c r="L30" s="46"/>
       <c r="M30" s="53" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="N30" s="54" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="O30" s="55"/>
       <c r="P30" s="56"/>
       <c r="Q30" s="73"/>
       <c r="R30" s="74" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="S30" s="75" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="T30" s="76"/>
       <c r="V30"/>
@@ -6878,7 +6864,7 @@
         <v>2</v>
       </c>
       <c r="B31" s="21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C31" s="22" t="s">
         <v>219</v>
@@ -6887,39 +6873,39 @@
         <v>220</v>
       </c>
       <c r="E31" s="24" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="F31" s="25" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="G31" s="26" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="H31" s="20" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="I31" s="51" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="J31" s="20" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="K31" s="52"/>
       <c r="L31" s="46"/>
       <c r="M31" s="53" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="N31" s="54" t="s">
-        <v>275</v>
+        <v>256</v>
       </c>
       <c r="O31" s="55"/>
       <c r="P31" s="56"/>
       <c r="Q31" s="73"/>
       <c r="R31" s="74" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="S31" s="75" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="T31" s="76"/>
       <c r="V31"/>
@@ -6929,7 +6915,7 @@
         <v>2</v>
       </c>
       <c r="B32" s="21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C32" s="22" t="s">
         <v>219</v>
@@ -6938,40 +6924,36 @@
         <v>220</v>
       </c>
       <c r="E32" s="24" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="F32" s="25" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="G32" s="26" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="H32" s="20" t="s">
-        <v>279</v>
-      </c>
-      <c r="I32" s="51" t="s">
-        <v>280</v>
-      </c>
-      <c r="J32" s="20" t="s">
-        <v>281</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="I32" s="51"/>
+      <c r="J32" s="20"/>
       <c r="K32" s="52"/>
       <c r="L32" s="46"/>
       <c r="M32" s="53" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="N32" s="54" t="s">
-        <v>256</v>
-      </c>
-      <c r="O32" s="55"/>
+        <v>289</v>
+      </c>
+      <c r="O32" s="55" t="s">
+        <v>290</v>
+      </c>
       <c r="P32" s="56"/>
       <c r="Q32" s="73"/>
       <c r="R32" s="74" t="s">
-        <v>278</v>
-      </c>
-      <c r="S32" s="75" t="s">
-        <v>283</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="S32" s="75"/>
       <c r="T32" s="76"/>
       <c r="V32"/>
     </row>
@@ -6980,7 +6962,7 @@
         <v>2</v>
       </c>
       <c r="B33" s="21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C33" s="22" t="s">
         <v>219</v>
@@ -6989,34 +6971,34 @@
         <v>220</v>
       </c>
       <c r="E33" s="24" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="F33" s="25" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="G33" s="26" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="H33" s="20" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="I33" s="51"/>
       <c r="J33" s="20"/>
       <c r="K33" s="52"/>
       <c r="L33" s="46"/>
       <c r="M33" s="53" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="N33" s="54" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="O33" s="55" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="P33" s="56"/>
       <c r="Q33" s="73"/>
       <c r="R33" s="74" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="S33" s="75"/>
       <c r="T33" s="76"/>
@@ -7027,7 +7009,7 @@
         <v>2</v>
       </c>
       <c r="B34" s="21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C34" s="22" t="s">
         <v>219</v>
@@ -7036,36 +7018,40 @@
         <v>220</v>
       </c>
       <c r="E34" s="24" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="F34" s="25" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="G34" s="26" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="H34" s="20" t="s">
-        <v>294</v>
-      </c>
-      <c r="I34" s="51"/>
-      <c r="J34" s="20"/>
+        <v>302</v>
+      </c>
+      <c r="I34" s="51" t="s">
+        <v>303</v>
+      </c>
+      <c r="J34" s="20" t="s">
+        <v>304</v>
+      </c>
       <c r="K34" s="52"/>
       <c r="L34" s="46"/>
       <c r="M34" s="53" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="N34" s="54" t="s">
-        <v>296</v>
-      </c>
-      <c r="O34" s="55" t="s">
-        <v>297</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="O34" s="55"/>
       <c r="P34" s="56"/>
       <c r="Q34" s="73"/>
       <c r="R34" s="74" t="s">
-        <v>298</v>
-      </c>
-      <c r="S34" s="75"/>
+        <v>301</v>
+      </c>
+      <c r="S34" s="75" t="s">
+        <v>307</v>
+      </c>
       <c r="T34" s="76"/>
       <c r="V34"/>
     </row>
@@ -7074,7 +7060,7 @@
         <v>2</v>
       </c>
       <c r="B35" s="21">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C35" s="22" t="s">
         <v>219</v>
@@ -7083,40 +7069,36 @@
         <v>220</v>
       </c>
       <c r="E35" s="24" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="F35" s="25" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="G35" s="26" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="H35" s="20" t="s">
-        <v>302</v>
-      </c>
-      <c r="I35" s="51" t="s">
-        <v>303</v>
-      </c>
-      <c r="J35" s="20" t="s">
-        <v>304</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="I35" s="51"/>
+      <c r="J35" s="20"/>
       <c r="K35" s="52"/>
       <c r="L35" s="46"/>
       <c r="M35" s="53" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="N35" s="54" t="s">
-        <v>306</v>
-      </c>
-      <c r="O35" s="55"/>
+        <v>313</v>
+      </c>
+      <c r="O35" s="55" t="s">
+        <v>314</v>
+      </c>
       <c r="P35" s="56"/>
       <c r="Q35" s="73"/>
       <c r="R35" s="74" t="s">
-        <v>301</v>
-      </c>
-      <c r="S35" s="75" t="s">
-        <v>307</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="S35" s="75"/>
       <c r="T35" s="76"/>
       <c r="V35"/>
     </row>
@@ -7125,7 +7107,7 @@
         <v>2</v>
       </c>
       <c r="B36" s="21">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C36" s="22" t="s">
         <v>219</v>
@@ -7134,179 +7116,87 @@
         <v>220</v>
       </c>
       <c r="E36" s="24" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="F36" s="25" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="G36" s="26" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="H36" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="I36" s="51"/>
-      <c r="J36" s="20"/>
+        <v>318</v>
+      </c>
+      <c r="I36" s="51" t="s">
+        <v>319</v>
+      </c>
+      <c r="J36" s="20" t="s">
+        <v>320</v>
+      </c>
       <c r="K36" s="52"/>
       <c r="L36" s="46"/>
       <c r="M36" s="53" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="N36" s="54" t="s">
-        <v>313</v>
-      </c>
-      <c r="O36" s="55" t="s">
-        <v>314</v>
-      </c>
+        <v>322</v>
+      </c>
+      <c r="O36" s="55"/>
       <c r="P36" s="56"/>
       <c r="Q36" s="73"/>
       <c r="R36" s="74" t="s">
-        <v>310</v>
-      </c>
-      <c r="S36" s="75"/>
+        <v>317</v>
+      </c>
+      <c r="S36" s="75" t="s">
+        <v>323</v>
+      </c>
       <c r="T36" s="76"/>
       <c r="V36"/>
     </row>
     <row r="37" spans="1:22" ht="70.05" customHeight="1">
-      <c r="A37" s="21">
+      <c r="A37" s="29">
         <v>2</v>
       </c>
-      <c r="B37" s="21">
-        <v>12</v>
-      </c>
-      <c r="C37" s="22" t="s">
+      <c r="B37" s="30">
+        <v>13</v>
+      </c>
+      <c r="C37" s="31" t="s">
         <v>219</v>
       </c>
-      <c r="D37" s="28" t="s">
+      <c r="D37" s="32" t="s">
         <v>220</v>
       </c>
-      <c r="E37" s="24" t="s">
-        <v>315</v>
-      </c>
-      <c r="F37" s="25" t="s">
-        <v>316</v>
-      </c>
-      <c r="G37" s="26" t="s">
-        <v>317</v>
-      </c>
-      <c r="H37" s="20" t="s">
-        <v>318</v>
-      </c>
-      <c r="I37" s="51" t="s">
-        <v>319</v>
-      </c>
-      <c r="J37" s="20" t="s">
-        <v>320</v>
-      </c>
-      <c r="K37" s="52"/>
-      <c r="L37" s="46"/>
-      <c r="M37" s="53" t="s">
-        <v>321</v>
-      </c>
-      <c r="N37" s="54" t="s">
-        <v>322</v>
-      </c>
-      <c r="O37" s="55"/>
-      <c r="P37" s="56"/>
-      <c r="Q37" s="73"/>
-      <c r="R37" s="74" t="s">
-        <v>317</v>
-      </c>
-      <c r="S37" s="75" t="s">
-        <v>323</v>
-      </c>
-      <c r="T37" s="76"/>
+      <c r="E37" s="33" t="s">
+        <v>324</v>
+      </c>
+      <c r="F37" s="34" t="s">
+        <v>325</v>
+      </c>
+      <c r="G37" s="35" t="s">
+        <v>326</v>
+      </c>
+      <c r="H37" s="36"/>
+      <c r="I37" s="57"/>
+      <c r="J37" s="58"/>
+      <c r="K37" s="59"/>
+      <c r="L37" s="60"/>
+      <c r="M37" s="61" t="s">
+        <v>327</v>
+      </c>
+      <c r="N37" s="62" t="s">
+        <v>328</v>
+      </c>
+      <c r="O37" s="63" t="s">
+        <v>329</v>
+      </c>
+      <c r="P37" s="64"/>
+      <c r="Q37" s="77"/>
+      <c r="R37" s="78" t="s">
+        <v>330</v>
+      </c>
+      <c r="S37" s="79"/>
+      <c r="T37" s="80"/>
       <c r="V37"/>
-    </row>
-    <row r="38" spans="1:22" ht="70.05" customHeight="1">
-      <c r="A38" s="29">
-        <v>2</v>
-      </c>
-      <c r="B38" s="30">
-        <v>13</v>
-      </c>
-      <c r="C38" s="31" t="s">
-        <v>219</v>
-      </c>
-      <c r="D38" s="32" t="s">
-        <v>220</v>
-      </c>
-      <c r="E38" s="33" t="s">
-        <v>324</v>
-      </c>
-      <c r="F38" s="34" t="s">
-        <v>325</v>
-      </c>
-      <c r="G38" s="35" t="s">
-        <v>326</v>
-      </c>
-      <c r="H38" s="36"/>
-      <c r="I38" s="57"/>
-      <c r="J38" s="58"/>
-      <c r="K38" s="59"/>
-      <c r="L38" s="60"/>
-      <c r="M38" s="61" t="s">
-        <v>327</v>
-      </c>
-      <c r="N38" s="62" t="s">
-        <v>328</v>
-      </c>
-      <c r="O38" s="63" t="s">
-        <v>329</v>
-      </c>
-      <c r="P38" s="64"/>
-      <c r="Q38" s="77"/>
-      <c r="R38" s="78" t="s">
-        <v>330</v>
-      </c>
-      <c r="S38" s="79"/>
-      <c r="T38" s="80"/>
-      <c r="V38"/>
-    </row>
-    <row r="39" spans="1:22" ht="70.05" customHeight="1">
-      <c r="A39" s="29">
-        <v>2</v>
-      </c>
-      <c r="B39" s="30">
-        <v>14</v>
-      </c>
-      <c r="C39" s="31" t="s">
-        <v>219</v>
-      </c>
-      <c r="D39" s="32" t="s">
-        <v>220</v>
-      </c>
-      <c r="E39" s="33" t="s">
-        <v>331</v>
-      </c>
-      <c r="F39" s="81" t="s">
-        <v>332</v>
-      </c>
-      <c r="G39" s="35" t="s">
-        <v>326</v>
-      </c>
-      <c r="H39" s="36"/>
-      <c r="I39" s="57"/>
-      <c r="J39" s="58"/>
-      <c r="K39" s="59"/>
-      <c r="L39" s="60"/>
-      <c r="M39" s="61" t="s">
-        <v>327</v>
-      </c>
-      <c r="N39" s="62" t="s">
-        <v>328</v>
-      </c>
-      <c r="O39" s="63" t="s">
-        <v>329</v>
-      </c>
-      <c r="P39" s="64"/>
-      <c r="Q39" s="77"/>
-      <c r="R39" s="78" t="s">
-        <v>330</v>
-      </c>
-      <c r="S39" s="79"/>
-      <c r="T39" s="80"/>
-      <c r="V39"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7"/>

--- a/quiz_questions.xlsx
+++ b/quiz_questions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NB-AJLS\ATP-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97E4C518-2FFC-405E-B5ED-B177118EBE7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D88533C0-5EFB-42EC-A719-DF415B516C33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1116" yWindow="1116" windowWidth="12372" windowHeight="10812" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="334">
   <si>
     <t>カテゴリNo.</t>
   </si>
@@ -4333,6 +4333,15 @@
   </si>
   <si>
     <t>ざいりゅうカード</t>
+  </si>
+  <si>
+    <t>あ</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>がっこう</t>
   </si>
 </sst>
 </file>
@@ -4769,7 +4778,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -5009,6 +5018,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5315,7 +5327,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V37"/>
+  <dimension ref="A1:V38"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="3.88671875" style="1" customWidth="1"/>
@@ -7198,6 +7210,51 @@
       <c r="T37" s="80"/>
       <c r="V37"/>
     </row>
+    <row r="38" spans="1:22" ht="70.05" customHeight="1">
+      <c r="A38" s="29">
+        <v>2</v>
+      </c>
+      <c r="B38" s="30">
+        <v>14</v>
+      </c>
+      <c r="C38" s="31" t="s">
+        <v>219</v>
+      </c>
+      <c r="D38" s="32" t="s">
+        <v>220</v>
+      </c>
+      <c r="E38" s="33" t="s">
+        <v>331</v>
+      </c>
+      <c r="F38" s="81" t="s">
+        <v>332</v>
+      </c>
+      <c r="G38" s="35" t="s">
+        <v>326</v>
+      </c>
+      <c r="H38" s="36"/>
+      <c r="I38" s="57"/>
+      <c r="J38" s="58"/>
+      <c r="K38" s="59"/>
+      <c r="L38" s="60"/>
+      <c r="M38" s="61" t="s">
+        <v>327</v>
+      </c>
+      <c r="N38" s="62" t="s">
+        <v>328</v>
+      </c>
+      <c r="O38" s="63" t="s">
+        <v>329</v>
+      </c>
+      <c r="P38" s="64"/>
+      <c r="Q38" s="77"/>
+      <c r="R38" s="78" t="s">
+        <v>333</v>
+      </c>
+      <c r="S38" s="79"/>
+      <c r="T38" s="80"/>
+      <c r="V38"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/quiz_questions.xlsx
+++ b/quiz_questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NB-AJLS\ATP-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D88533C0-5EFB-42EC-A719-DF415B516C33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB8A3A69-D2DE-4843-8A0F-4C163A07B15C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="331">
   <si>
     <t>カテゴリNo.</t>
   </si>
@@ -4333,15 +4333,6 @@
   </si>
   <si>
     <t>ざいりゅうカード</t>
-  </si>
-  <si>
-    <t>あ</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>がっこう</t>
   </si>
 </sst>
 </file>
@@ -4778,7 +4769,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -5018,9 +5009,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5327,7 +5315,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V38"/>
+  <dimension ref="A1:V37"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="3.88671875" style="1" customWidth="1"/>
@@ -7210,51 +7198,6 @@
       <c r="T37" s="80"/>
       <c r="V37"/>
     </row>
-    <row r="38" spans="1:22" ht="70.05" customHeight="1">
-      <c r="A38" s="29">
-        <v>2</v>
-      </c>
-      <c r="B38" s="30">
-        <v>14</v>
-      </c>
-      <c r="C38" s="31" t="s">
-        <v>219</v>
-      </c>
-      <c r="D38" s="32" t="s">
-        <v>220</v>
-      </c>
-      <c r="E38" s="33" t="s">
-        <v>331</v>
-      </c>
-      <c r="F38" s="81" t="s">
-        <v>332</v>
-      </c>
-      <c r="G38" s="35" t="s">
-        <v>326</v>
-      </c>
-      <c r="H38" s="36"/>
-      <c r="I38" s="57"/>
-      <c r="J38" s="58"/>
-      <c r="K38" s="59"/>
-      <c r="L38" s="60"/>
-      <c r="M38" s="61" t="s">
-        <v>327</v>
-      </c>
-      <c r="N38" s="62" t="s">
-        <v>328</v>
-      </c>
-      <c r="O38" s="63" t="s">
-        <v>329</v>
-      </c>
-      <c r="P38" s="64"/>
-      <c r="Q38" s="77"/>
-      <c r="R38" s="78" t="s">
-        <v>333</v>
-      </c>
-      <c r="S38" s="79"/>
-      <c r="T38" s="80"/>
-      <c r="V38"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
